--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Vanilla baseline is compared against the audited SB update. Tags: CAP = Cape states, TRN = Transvaal states, SAF = South African states, SWA = Namibian states.</t>
+          <t>Vanilla baseline is compared against the audited SB update. Tags: CAP = Cape states, TRN = Transvaal states, SAF = South African states, SWA = Namibian states. The progress block tracks the one-state-per-run counterfactual audit loop.</t>
         </is>
       </c>
     </row>
@@ -593,10 +593,10 @@
         <v>123</v>
       </c>
       <c r="C10" t="n">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>-52</v>
+        <v>-114</v>
       </c>
     </row>
     <row r="11">
@@ -893,10 +893,10 @@
         <v>33</v>
       </c>
       <c r="D28" t="n">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>35</v>
+        <v>-27</v>
       </c>
     </row>
     <row r="29">
@@ -1523,10 +1523,10 @@
         <v>123</v>
       </c>
       <c r="D58" t="n">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="E58" t="n">
-        <v>-52</v>
+        <v>-114</v>
       </c>
     </row>
     <row r="59">
@@ -2051,6 +2051,314 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84"/>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>State pass progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Pass order</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>Completed rows</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>Changed rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Cape Colony</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>accepted</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>30</v>
+      </c>
+      <c r="E87" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Northern Cape</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>2</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>accepted</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>30</v>
+      </c>
+      <c r="E88" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Eastern Cape</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>3</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>not started</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>West Transvaal</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>4</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>not started</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Eastern Transvaal</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>5</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>not started</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Northern Transvaal</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>6</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>not started</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Transorangia</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>7</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>not started</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Drakensberg</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>8</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>not started</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Botswana</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>9</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>not started</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Lourenço Marques</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>10</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>not started</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Zambezi</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>11</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>not started</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Hereroland</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>12</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>not started</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Namaqualand</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>13</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>not started</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2069,14 +2377,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2096,7 +2405,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Final column shows the proposed SB update. Arable-resource rows are yes/no gameplay availability, while capped rows are numeric caps.</t>
+          <t>The SB update column shows the audited value and the Basis column shows whether that row is historical, counterfactual, an exception, or unchanged.</t>
         </is>
       </c>
     </row>
@@ -2181,6 +2490,11 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
           <t>Delta / change</t>
         </is>
       </c>
@@ -2202,7 +2516,12 @@
       <c r="D13" t="n">
         <v>5</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>-35</v>
       </c>
     </row>
@@ -2229,6 +2548,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -2256,6 +2580,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -2283,6 +2612,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -2310,6 +2644,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -2337,6 +2676,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -2364,6 +2708,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -2391,6 +2740,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -2418,6 +2772,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -2445,6 +2804,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -2472,6 +2836,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -2499,6 +2868,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -2526,6 +2900,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -2553,6 +2932,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -2580,6 +2964,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -2607,6 +2996,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -2628,7 +3022,12 @@
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>-48</v>
       </c>
     </row>
@@ -2649,7 +3048,12 @@
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2670,7 +3074,12 @@
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2691,7 +3100,12 @@
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2712,7 +3126,12 @@
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2733,7 +3152,12 @@
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2754,7 +3178,12 @@
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2775,7 +3204,12 @@
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>-5</v>
       </c>
     </row>
@@ -2796,7 +3230,12 @@
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2817,7 +3256,12 @@
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2838,7 +3282,12 @@
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2859,7 +3308,12 @@
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2880,7 +3334,12 @@
       <c r="D41" t="n">
         <v>0</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2901,15 +3360,20 @@
       <c r="D42" t="n">
         <v>0</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2921,7 +3385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2929,6 +3393,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2948,7 +3413,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Final column shows the proposed SB update. Arable-resource rows are yes/no gameplay availability, while capped rows are numeric caps.</t>
+          <t>The SB update column shows the audited value and the Basis column shows whether that row is historical, counterfactual, an exception, or unchanged.</t>
         </is>
       </c>
     </row>
@@ -3033,6 +3498,11 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
           <t>Delta / change</t>
         </is>
       </c>
@@ -3054,7 +3524,12 @@
       <c r="D13" t="n">
         <v>30</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Counterfactual</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -3081,6 +3556,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -3108,6 +3588,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -3135,6 +3620,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -3162,6 +3652,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -3189,6 +3684,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -3216,6 +3716,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -3243,6 +3748,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -3270,6 +3780,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -3297,6 +3812,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -3324,6 +3844,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -3351,6 +3876,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -3378,6 +3908,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -3405,6 +3940,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -3432,6 +3972,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -3459,6 +4004,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -3480,7 +4030,12 @@
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>-40</v>
       </c>
     </row>
@@ -3501,7 +4056,12 @@
       <c r="D30" t="n">
         <v>2</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>-6</v>
       </c>
     </row>
@@ -3522,7 +4082,12 @@
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3543,7 +4108,12 @@
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3564,7 +4134,12 @@
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3585,7 +4160,12 @@
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3606,7 +4186,12 @@
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3627,7 +4212,12 @@
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>-9</v>
       </c>
     </row>
@@ -3648,7 +4238,12 @@
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3669,7 +4264,12 @@
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3690,7 +4290,12 @@
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3711,7 +4316,12 @@
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3732,7 +4342,12 @@
       <c r="D41" t="n">
         <v>0</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3753,15 +4368,20 @@
       <c r="D42" t="n">
         <v>0</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
         <v>-16</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3773,7 +4393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -3781,6 +4401,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3800,7 +4421,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Final column shows the proposed SB update. Arable-resource rows are yes/no gameplay availability, while capped rows are numeric caps.</t>
+          <t>The SB update column shows the audited value and the Basis column shows whether that row is historical, counterfactual, an exception, or unchanged.</t>
         </is>
       </c>
     </row>
@@ -3885,6 +4506,11 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
           <t>Delta / change</t>
         </is>
       </c>
@@ -3906,7 +4532,12 @@
       <c r="D13" t="n">
         <v>25</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Counterfactual</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>-45</v>
       </c>
     </row>
@@ -3933,6 +4564,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -3960,6 +4596,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -3987,6 +4628,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -4014,6 +4660,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -4041,6 +4692,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -4068,6 +4724,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -4095,6 +4756,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -4122,6 +4788,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -4149,6 +4820,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -4176,6 +4852,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -4203,6 +4884,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -4230,6 +4916,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -4257,6 +4948,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -4284,6 +4980,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -4311,6 +5012,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -4332,7 +5038,12 @@
       <c r="D29" t="n">
         <v>4</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>-40</v>
       </c>
     </row>
@@ -4353,7 +5064,12 @@
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4374,7 +5090,12 @@
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4395,7 +5116,12 @@
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4416,7 +5142,12 @@
       <c r="D33" t="n">
         <v>1</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4437,7 +5168,12 @@
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4458,7 +5194,12 @@
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4479,7 +5220,12 @@
       <c r="D36" t="n">
         <v>3</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Counterfactual</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>-8</v>
       </c>
     </row>
@@ -4500,7 +5246,12 @@
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4521,7 +5272,12 @@
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4542,7 +5298,12 @@
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4563,7 +5324,12 @@
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4584,7 +5350,12 @@
       <c r="D41" t="n">
         <v>0</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4605,15 +5376,20 @@
       <c r="D42" t="n">
         <v>0</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
         <v>-16</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4625,14 +5401,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4652,7 +5429,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Final column shows the proposed SB update. Arable-resource rows are yes/no gameplay availability, while capped rows are numeric caps.</t>
+          <t>The SB update column shows the audited value and the Basis column shows whether that row is historical, counterfactual, an exception, or unchanged.</t>
         </is>
       </c>
     </row>
@@ -4737,6 +5514,11 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
           <t>Delta / change</t>
         </is>
       </c>
@@ -4758,7 +5540,12 @@
       <c r="D13" t="n">
         <v>4</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>-36</v>
       </c>
     </row>
@@ -4785,6 +5572,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -4812,6 +5604,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -4839,6 +5636,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -4866,6 +5668,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -4893,6 +5700,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -4920,6 +5732,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -4947,6 +5764,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -4974,6 +5796,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -5001,6 +5828,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -5028,6 +5860,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -5055,6 +5892,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -5082,6 +5924,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -5109,6 +5956,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -5136,6 +5988,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -5163,6 +6020,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -5184,7 +6046,12 @@
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>-40</v>
       </c>
     </row>
@@ -5205,7 +6072,12 @@
       <c r="D30" t="n">
         <v>11</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5226,7 +6098,12 @@
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5247,7 +6124,12 @@
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5268,7 +6150,12 @@
       <c r="D33" t="n">
         <v>39</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>39</v>
       </c>
     </row>
@@ -5289,7 +6176,12 @@
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5310,7 +6202,12 @@
       <c r="D35" t="n">
         <v>2</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5331,7 +6228,12 @@
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>-2</v>
       </c>
     </row>
@@ -5352,7 +6254,12 @@
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5373,7 +6280,12 @@
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5394,7 +6306,12 @@
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5415,7 +6332,12 @@
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5436,7 +6358,12 @@
       <c r="D41" t="n">
         <v>0</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5457,15 +6384,20 @@
       <c r="D42" t="n">
         <v>0</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5477,7 +6409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -5485,6 +6417,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5504,7 +6437,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Final column shows the proposed SB update. Arable-resource rows are yes/no gameplay availability, while capped rows are numeric caps.</t>
+          <t>The SB update column shows the audited value and the Basis column shows whether that row is historical, counterfactual, an exception, or unchanged.</t>
         </is>
       </c>
     </row>
@@ -5589,6 +6522,11 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
           <t>Delta / change</t>
         </is>
       </c>
@@ -5610,7 +6548,12 @@
       <c r="D13" t="n">
         <v>1</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Counterfactual</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>-29</v>
       </c>
     </row>
@@ -5637,6 +6580,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -5664,6 +6612,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -5691,6 +6644,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -5718,6 +6676,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -5745,6 +6708,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -5772,6 +6740,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -5799,6 +6772,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -5826,6 +6804,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -5853,6 +6836,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -5880,6 +6868,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -5907,6 +6900,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -5934,6 +6932,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -5961,6 +6964,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -5988,6 +6996,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -6015,6 +7028,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -6036,7 +7054,12 @@
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>-32</v>
       </c>
     </row>
@@ -6057,7 +7080,12 @@
       <c r="D30" t="n">
         <v>1</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>-6</v>
       </c>
     </row>
@@ -6078,7 +7106,12 @@
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6099,7 +7132,12 @@
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6120,7 +7158,12 @@
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6141,7 +7184,12 @@
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6162,7 +7210,12 @@
       <c r="D35" t="n">
         <v>2</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6183,7 +7236,12 @@
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>-4</v>
       </c>
     </row>
@@ -6204,7 +7262,12 @@
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6225,7 +7288,12 @@
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6246,7 +7314,12 @@
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6267,7 +7340,12 @@
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6288,7 +7366,12 @@
       <c r="D41" t="n">
         <v>0</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6309,15 +7392,20 @@
       <c r="D42" t="n">
         <v>0</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6329,7 +7417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -6337,6 +7425,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6356,7 +7445,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Final column shows the proposed SB update. Arable-resource rows are yes/no gameplay availability, while capped rows are numeric caps.</t>
+          <t>The SB update column shows the audited value and the Basis column shows whether that row is historical, counterfactual, an exception, or unchanged.</t>
         </is>
       </c>
     </row>
@@ -6441,6 +7530,11 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
           <t>Delta / change</t>
         </is>
       </c>
@@ -6462,7 +7556,12 @@
       <c r="D13" t="n">
         <v>41</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>-9</v>
       </c>
     </row>
@@ -6489,6 +7588,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -6516,6 +7620,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -6543,6 +7652,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -6570,6 +7684,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -6597,6 +7716,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -6624,6 +7748,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -6651,6 +7780,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -6678,6 +7812,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -6705,6 +7844,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -6732,6 +7876,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -6759,6 +7908,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -6786,6 +7940,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -6813,6 +7972,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -6840,6 +8004,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -6867,6 +8036,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -6888,7 +8062,12 @@
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6909,7 +8088,12 @@
       <c r="D30" t="n">
         <v>12</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6930,7 +8114,12 @@
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6951,7 +8140,12 @@
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6972,7 +8166,12 @@
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6993,7 +8192,12 @@
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7014,7 +8218,12 @@
       <c r="D35" t="n">
         <v>4</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7035,7 +8244,12 @@
       <c r="D36" t="n">
         <v>3</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Counterfactual</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>-5</v>
       </c>
     </row>
@@ -7056,7 +8270,12 @@
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7077,7 +8296,12 @@
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7098,7 +8322,12 @@
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7119,7 +8348,12 @@
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7140,7 +8374,12 @@
       <c r="D41" t="n">
         <v>0</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7161,15 +8400,20 @@
       <c r="D42" t="n">
         <v>0</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7181,7 +8425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -7189,6 +8433,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7208,7 +8453,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Final column shows the proposed SB update. Arable-resource rows are yes/no gameplay availability, while capped rows are numeric caps.</t>
+          <t>The SB update column shows the audited value and the Basis column shows whether that row is historical, counterfactual, an exception, or unchanged.</t>
         </is>
       </c>
     </row>
@@ -7249,7 +8494,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -7259,7 +8504,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="10"/>
@@ -7293,6 +8538,11 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
           <t>Delta / change</t>
         </is>
       </c>
@@ -7314,7 +8564,12 @@
       <c r="D13" t="n">
         <v>11</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>-29</v>
       </c>
     </row>
@@ -7341,6 +8596,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -7368,6 +8628,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -7395,6 +8660,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -7422,6 +8692,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -7449,6 +8724,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -7476,6 +8756,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -7503,6 +8788,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -7530,6 +8820,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -7557,6 +8852,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -7584,6 +8884,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -7611,6 +8916,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -7638,6 +8948,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -7665,6 +8980,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -7692,6 +9012,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -7719,6 +9044,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -7740,7 +9070,12 @@
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7761,7 +9096,12 @@
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7782,7 +9122,12 @@
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7801,10 +9146,15 @@
         <v>33</v>
       </c>
       <c r="D32" t="n">
-        <v>68</v>
-      </c>
-      <c r="E32" t="n">
-        <v>35</v>
+        <v>6</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Counterfactual</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>-27</v>
       </c>
     </row>
     <row r="33">
@@ -7824,7 +9174,12 @@
       <c r="D33" t="n">
         <v>11</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Counterfactual</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7845,7 +9200,12 @@
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7866,7 +9226,12 @@
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7887,7 +9252,12 @@
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>-2</v>
       </c>
     </row>
@@ -7908,7 +9278,12 @@
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>-1</v>
       </c>
     </row>
@@ -7929,7 +9304,12 @@
       <c r="D38" t="n">
         <v>20</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
         <v>12</v>
       </c>
     </row>
@@ -7950,7 +9330,12 @@
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7971,7 +9356,12 @@
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7992,7 +9382,12 @@
       <c r="D41" t="n">
         <v>0</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8013,15 +9408,20 @@
       <c r="D42" t="n">
         <v>0</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8033,14 +9433,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8060,7 +9461,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Final column shows the proposed SB update. Arable-resource rows are yes/no gameplay availability, while capped rows are numeric caps.</t>
+          <t>The SB update column shows the audited value and the Basis column shows whether that row is historical, counterfactual, an exception, or unchanged.</t>
         </is>
       </c>
     </row>
@@ -8145,6 +9546,11 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
           <t>Delta / change</t>
         </is>
       </c>
@@ -8166,7 +9572,12 @@
       <c r="D13" t="n">
         <v>45</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>-15</v>
       </c>
     </row>
@@ -8193,6 +9604,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -8220,6 +9636,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -8247,6 +9668,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -8274,6 +9700,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -8301,6 +9732,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -8328,6 +9764,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -8355,6 +9796,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -8382,6 +9828,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -8409,6 +9860,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -8436,6 +9892,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -8463,6 +9924,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -8490,6 +9956,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -8517,6 +9988,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -8544,6 +10020,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -8571,6 +10052,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -8592,7 +10078,12 @@
       <c r="D29" t="n">
         <v>1</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>-55</v>
       </c>
     </row>
@@ -8613,7 +10104,12 @@
       <c r="D30" t="n">
         <v>1</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>-7</v>
       </c>
     </row>
@@ -8634,7 +10130,12 @@
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8655,7 +10156,12 @@
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8676,7 +10182,12 @@
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8697,7 +10208,12 @@
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8718,7 +10234,12 @@
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8739,7 +10260,12 @@
       <c r="D36" t="n">
         <v>8</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>-1</v>
       </c>
     </row>
@@ -8760,7 +10286,12 @@
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8781,7 +10312,12 @@
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8802,7 +10338,12 @@
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8823,7 +10364,12 @@
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8844,7 +10390,12 @@
       <c r="D41" t="n">
         <v>0</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8865,15 +10416,20 @@
       <c r="D42" t="n">
         <v>0</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8885,7 +10441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -8893,6 +10449,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8912,7 +10469,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Final column shows the proposed SB update. Arable-resource rows are yes/no gameplay availability, while capped rows are numeric caps.</t>
+          <t>The SB update column shows the audited value and the Basis column shows whether that row is historical, counterfactual, an exception, or unchanged.</t>
         </is>
       </c>
     </row>
@@ -8997,6 +10554,11 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
           <t>Delta / change</t>
         </is>
       </c>
@@ -9018,7 +10580,12 @@
       <c r="D13" t="n">
         <v>15</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Counterfactual</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>-35</v>
       </c>
     </row>
@@ -9045,6 +10612,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -9072,6 +10644,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -9099,6 +10676,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -9126,6 +10708,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -9153,6 +10740,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -9180,6 +10772,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -9207,6 +10804,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -9234,6 +10836,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -9261,6 +10868,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -9288,6 +10900,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -9315,6 +10932,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -9342,6 +10964,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -9369,6 +10996,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -9396,6 +11028,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -9423,6 +11060,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -9444,7 +11086,12 @@
       <c r="D29" t="n">
         <v>4</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -9465,7 +11112,12 @@
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9486,7 +11138,12 @@
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9507,7 +11164,12 @@
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>-60</v>
       </c>
     </row>
@@ -9528,7 +11190,12 @@
       <c r="D33" t="n">
         <v>3</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9549,7 +11216,12 @@
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9570,7 +11242,12 @@
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9591,7 +11268,12 @@
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>-5</v>
       </c>
     </row>
@@ -9612,7 +11294,12 @@
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9633,7 +11320,12 @@
       <c r="D38" t="n">
         <v>94</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
         <v>82</v>
       </c>
     </row>
@@ -9654,7 +11346,12 @@
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9675,7 +11372,12 @@
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9696,7 +11398,12 @@
       <c r="D41" t="n">
         <v>0</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9717,15 +11424,20 @@
       <c r="D42" t="n">
         <v>0</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9737,7 +11449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -9745,6 +11457,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9764,7 +11477,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Final column shows the proposed SB update. Arable-resource rows are yes/no gameplay availability, while capped rows are numeric caps.</t>
+          <t>The SB update column shows the audited value and the Basis column shows whether that row is historical, counterfactual, an exception, or unchanged.</t>
         </is>
       </c>
     </row>
@@ -9849,6 +11562,11 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
           <t>Delta / change</t>
         </is>
       </c>
@@ -9870,7 +11588,12 @@
       <c r="D13" t="n">
         <v>35</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Counterfactual</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>-15</v>
       </c>
     </row>
@@ -9897,6 +11620,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -9924,6 +11652,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -9951,6 +11684,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -9978,6 +11716,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -10005,6 +11748,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -10032,6 +11780,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -10059,6 +11812,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -10086,6 +11844,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -10113,6 +11876,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -10140,6 +11908,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -10167,6 +11940,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -10194,6 +11972,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -10221,6 +12004,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -10248,6 +12036,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -10275,6 +12068,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -10296,7 +12094,12 @@
       <c r="D29" t="n">
         <v>104</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10317,7 +12120,12 @@
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10338,7 +12146,12 @@
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10359,7 +12172,12 @@
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>-60</v>
       </c>
     </row>
@@ -10380,7 +12198,12 @@
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10401,7 +12224,12 @@
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10422,7 +12250,12 @@
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10443,7 +12276,12 @@
       <c r="D36" t="n">
         <v>11</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>6</v>
       </c>
     </row>
@@ -10464,7 +12302,12 @@
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10485,7 +12328,12 @@
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
         <v>-12</v>
       </c>
     </row>
@@ -10506,7 +12354,12 @@
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10527,7 +12380,12 @@
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10548,7 +12406,12 @@
       <c r="D41" t="n">
         <v>0</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10569,15 +12432,20 @@
       <c r="D42" t="n">
         <v>0</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10589,14 +12457,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10616,7 +12485,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Final column shows the proposed SB update. Arable-resource rows are yes/no gameplay availability, while capped rows are numeric caps.</t>
+          <t>The SB update column shows the audited value and the Basis column shows whether that row is historical, counterfactual, an exception, or unchanged.</t>
         </is>
       </c>
     </row>
@@ -10701,6 +12570,11 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
           <t>Delta / change</t>
         </is>
       </c>
@@ -10722,7 +12596,12 @@
       <c r="D13" t="n">
         <v>18</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>-32</v>
       </c>
     </row>
@@ -10749,6 +12628,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -10776,6 +12660,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -10803,6 +12692,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -10830,6 +12724,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -10857,6 +12756,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -10884,6 +12788,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -10911,6 +12820,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -10938,6 +12852,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -10965,6 +12884,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -10992,6 +12916,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -11019,6 +12948,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -11046,6 +12980,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -11073,6 +13012,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -11100,6 +13044,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -11127,6 +13076,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -11148,7 +13102,12 @@
       <c r="D29" t="n">
         <v>8</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>-96</v>
       </c>
     </row>
@@ -11169,7 +13128,12 @@
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11190,7 +13154,12 @@
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11211,7 +13180,12 @@
       <c r="D32" t="n">
         <v>3</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>-57</v>
       </c>
     </row>
@@ -11232,7 +13206,12 @@
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11253,7 +13232,12 @@
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11274,7 +13258,12 @@
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11295,7 +13284,12 @@
       <c r="D36" t="n">
         <v>1</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>-4</v>
       </c>
     </row>
@@ -11316,7 +13310,12 @@
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11337,7 +13336,12 @@
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
         <v>-12</v>
       </c>
     </row>
@@ -11358,7 +13362,12 @@
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11379,7 +13388,12 @@
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11400,7 +13414,12 @@
       <c r="D41" t="n">
         <v>0</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11421,15 +13440,20 @@
       <c r="D42" t="n">
         <v>0</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11441,14 +13465,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11468,7 +13493,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Final column shows the proposed SB update. Arable-resource rows are yes/no gameplay availability, while capped rows are numeric caps.</t>
+          <t>The SB update column shows the audited value and the Basis column shows whether that row is historical, counterfactual, an exception, or unchanged.</t>
         </is>
       </c>
     </row>
@@ -11553,6 +13578,11 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
           <t>Delta / change</t>
         </is>
       </c>
@@ -11574,7 +13604,12 @@
       <c r="D13" t="n">
         <v>30</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>-10</v>
       </c>
     </row>
@@ -11601,6 +13636,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -11628,6 +13668,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -11655,6 +13700,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -11682,6 +13732,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -11709,6 +13764,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -11736,6 +13796,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -11763,6 +13828,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -11790,6 +13860,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -11817,6 +13892,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -11844,6 +13924,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -11871,6 +13956,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -11898,6 +13988,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -11925,6 +14020,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -11952,6 +14052,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -11979,6 +14084,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -12000,7 +14110,12 @@
       <c r="D29" t="n">
         <v>1</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>-59</v>
       </c>
     </row>
@@ -12021,7 +14136,12 @@
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12042,7 +14162,12 @@
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12063,7 +14188,12 @@
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>-30</v>
       </c>
     </row>
@@ -12084,7 +14214,12 @@
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12105,7 +14240,12 @@
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12126,7 +14266,12 @@
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12147,7 +14292,12 @@
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>-7</v>
       </c>
     </row>
@@ -12168,7 +14318,12 @@
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12189,7 +14344,12 @@
       <c r="D38" t="n">
         <v>3</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
         <v>-13</v>
       </c>
     </row>
@@ -12210,7 +14370,12 @@
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12231,7 +14396,12 @@
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12252,7 +14422,12 @@
       <c r="D41" t="n">
         <v>0</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12273,15 +14448,20 @@
       <c r="D42" t="n">
         <v>0</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12293,14 +14473,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12320,7 +14501,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Final column shows the proposed SB update. Arable-resource rows are yes/no gameplay availability, while capped rows are numeric caps.</t>
+          <t>The SB update column shows the audited value and the Basis column shows whether that row is historical, counterfactual, an exception, or unchanged.</t>
         </is>
       </c>
     </row>
@@ -12405,6 +14586,11 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
           <t>Delta / change</t>
         </is>
       </c>
@@ -12426,7 +14612,12 @@
       <c r="D13" t="n">
         <v>9</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>-31</v>
       </c>
     </row>
@@ -12453,6 +14644,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -12480,6 +14676,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -12507,6 +14708,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -12534,6 +14740,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -12561,6 +14772,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Added</t>
         </is>
       </c>
@@ -12588,6 +14804,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -12615,6 +14836,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -12642,6 +14868,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -12669,6 +14900,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -12696,6 +14932,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -12723,6 +14964,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>Removed</t>
         </is>
       </c>
@@ -12750,6 +14996,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -12777,6 +15028,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -12804,6 +15060,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -12831,6 +15092,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>No change</t>
         </is>
       </c>
@@ -12852,7 +15118,12 @@
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>-72</v>
       </c>
     </row>
@@ -12873,7 +15144,12 @@
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>-5</v>
       </c>
     </row>
@@ -12894,7 +15170,12 @@
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12915,7 +15196,12 @@
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12936,7 +15222,12 @@
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12957,7 +15248,12 @@
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12978,7 +15274,12 @@
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12999,7 +15300,12 @@
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>-11</v>
       </c>
     </row>
@@ -13020,7 +15326,12 @@
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13041,7 +15352,12 @@
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13062,7 +15378,12 @@
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13083,7 +15404,12 @@
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13104,7 +15430,12 @@
       <c r="D41" t="n">
         <v>0</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13125,15 +15456,20 @@
       <c r="D42" t="n">
         <v>0</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cape Colony" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Northern Cape" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eastern Cape" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="West Transvaal" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eastern Transvaal" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Northern Transvaal" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transorangia" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drakensberg" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Botswana" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lourenço Marques" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zambezi" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hereroland" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Namaqualand" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Cape Colony" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Northern Cape" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Eastern Cape" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="West Transvaal" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Eastern Transvaal" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Northern Transvaal" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Transorangia" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Drakensberg" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Botswana" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Lourenço Marques" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Zambezi" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Hereroland" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Namaqualand" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2142,14 +2142,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>not started</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90">
@@ -9695,17 +9695,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Unchanged</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Removed</t>
+          <t>No change</t>
         </is>
       </c>
     </row>

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cape Colony" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Northern Cape" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Eastern Cape" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="West Transvaal" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Eastern Transvaal" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Northern Transvaal" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Transorangia" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Drakensberg" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Botswana" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Lourenço Marques" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Zambezi" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Hereroland" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Namaqualand" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cape Colony" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Northern Cape" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eastern Cape" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="West Transvaal" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eastern Transvaal" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Northern Transvaal" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transorangia" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drakensberg" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Botswana" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lourenço Marques" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zambezi" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hereroland" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Namaqualand" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -609,10 +609,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D11" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12">
@@ -1229,10 +1229,10 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1544,10 +1544,10 @@
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E59" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60">
@@ -2163,14 +2163,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>not started</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91">
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9">
@@ -10520,7 +10520,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-115</v>
+        <v>-118</v>
       </c>
     </row>
     <row r="10"/>
@@ -11188,15 +11188,15 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Exception</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -689,10 +689,10 @@
         <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D16" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17">
@@ -1334,10 +1334,10 @@
         <v>12</v>
       </c>
       <c r="D49" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E49" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50">
@@ -1649,10 +1649,10 @@
         <v>36</v>
       </c>
       <c r="D64" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E64" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65">
@@ -2184,14 +2184,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>not started</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92">
@@ -11518,7 +11518,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9">
@@ -11528,7 +11528,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-81</v>
+        <v>-77</v>
       </c>
     </row>
     <row r="10"/>
@@ -12326,7 +12326,7 @@
         <v>12</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="39">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -2205,14 +2205,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>not started</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93">
@@ -12464,7 +12464,7 @@
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Counterfactual</t>
         </is>
       </c>
       <c r="F29" t="n">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -2226,14 +2226,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>not started</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="94">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -2247,14 +2247,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>not started</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -689,10 +689,10 @@
         <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D16" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17">
@@ -2268,14 +2268,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>not started</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-88</v>
+        <v>-87</v>
       </c>
     </row>
     <row r="10"/>
@@ -3254,7 +3254,7 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -2289,14 +2289,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>not started</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cape Colony" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Northern Cape" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eastern Cape" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="West Transvaal" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eastern Transvaal" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Northern Transvaal" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transorangia" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drakensberg" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Botswana" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lourenço Marques" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zambezi" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hereroland" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Namaqualand" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Cape Colony" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Northern Cape" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Eastern Cape" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="West Transvaal" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Eastern Transvaal" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Northern Transvaal" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Transorangia" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Drakensberg" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Botswana" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Lourenço Marques" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Zambezi" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Hereroland" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Namaqualand" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2180,14 +2180,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>not started</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cape Colony" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Northern Cape" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Eastern Cape" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="West Transvaal" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Eastern Transvaal" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Northern Transvaal" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Transorangia" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Drakensberg" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Botswana" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Lourenço Marques" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Zambezi" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Hereroland" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Namaqualand" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cape Colony" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Northern Cape" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eastern Cape" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="West Transvaal" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eastern Transvaal" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Northern Transvaal" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transorangia" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drakensberg" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Botswana" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lourenço Marques" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zambezi" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hereroland" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Namaqualand" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2201,14 +2201,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>not started</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -2222,14 +2222,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>not started</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -2243,14 +2243,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>not started</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -2264,14 +2264,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>not started</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -2285,14 +2285,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>not started</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -2306,14 +2306,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>not started</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="102">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -2327,14 +2327,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>not started</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -2348,14 +2348,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>not started</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E103" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -2369,14 +2369,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>not started</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="105">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -15,12 +15,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eastern Transvaal" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Northern Transvaal" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transorangia" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drakensberg" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Botswana" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lourenço Marques" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zambezi" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hereroland" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Namaqualand" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zululand" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drakensberg" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Botswana" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lourenço Marques" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zambezi" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hereroland" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Namaqualand" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -465,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E107"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -606,13 +607,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C14" t="n">
-        <v>272</v>
+        <v>327</v>
       </c>
       <c r="D14" t="n">
-        <v>-268</v>
+        <v>-211</v>
       </c>
     </row>
     <row r="15">
@@ -622,13 +623,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>496</v>
+        <v>472</v>
       </c>
       <c r="C15" t="n">
         <v>125</v>
       </c>
       <c r="D15" t="n">
-        <v>-371</v>
+        <v>-347</v>
       </c>
     </row>
     <row r="16">
@@ -638,13 +639,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="n">
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="17">
@@ -734,13 +735,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C22" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D22" t="n">
-        <v>-45</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="23">
@@ -889,10 +890,10 @@
         <v>150</v>
       </c>
       <c r="D32" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E32" t="n">
-        <v>-52</v>
+        <v>-46</v>
       </c>
     </row>
     <row r="33">
@@ -1204,10 +1205,10 @@
         <v>50</v>
       </c>
       <c r="D47" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E47" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48">
@@ -1519,10 +1520,10 @@
         <v>240</v>
       </c>
       <c r="D62" t="n">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="E62" t="n">
-        <v>-43</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="63">
@@ -1834,10 +1835,10 @@
         <v>70</v>
       </c>
       <c r="D77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E77" t="n">
-        <v>-65</v>
+        <v>-64</v>
       </c>
     </row>
     <row r="78">
@@ -2201,14 +2202,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>not started</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -2222,14 +2223,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>not started</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -2243,14 +2244,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>not started</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -2264,14 +2265,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>not started</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -2285,14 +2286,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>not started</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2306,20 +2307,20 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>not started</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Drakensberg</t>
+          <t>Zululand</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -2327,20 +2328,20 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>not started</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Drakensberg</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -2348,20 +2349,20 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>not started</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Lourenço Marques</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -2369,20 +2370,20 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>not started</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Zambezi</t>
+          <t>Lourenço Marques</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -2403,7 +2404,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Hereroland</t>
+          <t>Zambezi</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -2424,7 +2425,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Namaqualand</t>
+          <t>Hereroland</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -2439,6 +2440,27 @@
         <v>0</v>
       </c>
       <c r="E107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Namaqualand</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>14</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>not started</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2471,14 +2493,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Botswana - vanilla baseline and proposed SB update</t>
+          <t>Drakensberg - vanilla baseline and proposed SB update</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SB target mapping: Botswana -&gt; STATE_BOTSWANA | Vanilla proxy: Botswana -&gt; STATE_BOTSWANA</t>
+          <t>SB target mapping: Drakensberg -&gt; STATE_DRAKENSBERG | Vanilla proxy: Zululand -&gt; STATE_ZULULAND</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2545,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>93</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9">
@@ -2533,7 +2555,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -2543,7 +2565,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-87</v>
+        <v>-118</v>
       </c>
     </row>
     <row r="11"/>
@@ -2601,7 +2623,7 @@
         <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -2609,7 +2631,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-35</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="15">
@@ -2630,17 +2652,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Unchanged</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>No change</t>
+          <t>Added</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2711,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2699,12 +2721,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Unchanged</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>No change</t>
+          <t>Removed</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2743,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2731,12 +2753,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Unchanged</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>No change</t>
+          <t>Removed</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2903,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2891,12 +2913,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Unchanged</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>No change</t>
+          <t>Removed</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2967,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2955,12 +2977,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Unchanged</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>No change</t>
+          <t>Removed</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3126,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -3115,7 +3137,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>-48</v>
+        <v>-72</v>
       </c>
     </row>
     <row r="31">
@@ -3130,7 +3152,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -3141,7 +3163,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="32">
@@ -3286,7 +3308,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -3297,7 +3319,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-5</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="38">
@@ -3341,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -3349,7 +3371,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3480,21 +3502,21 @@
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Lourenço Marques - vanilla baseline and proposed SB update</t>
+          <t>Botswana - vanilla baseline and proposed SB update</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SB target mapping: Lourenço Marques -&gt; STATE_LOURENCO_MARQUES | Vanilla proxy: Lourenço Marques -&gt; STATE_LOURENCO_MARQUES</t>
+          <t>SB target mapping: Botswana -&gt; STATE_BOTSWANA | Vanilla proxy: Botswana -&gt; STATE_BOTSWANA</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3561,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>153</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9">
@@ -3549,7 +3571,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -3559,7 +3581,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-105</v>
+        <v>-86</v>
       </c>
     </row>
     <row r="11"/>
@@ -3614,18 +3636,18 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Counterfactual</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-50</v>
+        <v>-34</v>
       </c>
     </row>
     <row r="15">
@@ -3737,7 +3759,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3747,12 +3769,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Unchanged</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Removed</t>
+          <t>No change</t>
         </is>
       </c>
     </row>
@@ -3833,12 +3855,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3865,7 +3887,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3875,12 +3897,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Unchanged</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Removed</t>
+          <t>No change</t>
         </is>
       </c>
     </row>
@@ -3897,12 +3919,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3929,7 +3951,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3939,12 +3961,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Unchanged</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Removed</t>
+          <t>No change</t>
         </is>
       </c>
     </row>
@@ -3961,12 +3983,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3998,17 +4020,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Unchanged</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>No change</t>
         </is>
       </c>
     </row>
@@ -4025,7 +4047,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4035,12 +4057,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Unchanged</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Removed</t>
+          <t>No change</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4142,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -4131,7 +4153,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>-40</v>
+        <v>-48</v>
       </c>
     </row>
     <row r="31">
@@ -4146,18 +4168,18 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Exception</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -4302,7 +4324,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -4313,7 +4335,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-9</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="38">
@@ -4357,7 +4379,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -4365,7 +4387,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -4458,14 +4480,14 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Counterfactual</t>
+          <t>Exception</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -4503,14 +4525,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zambezi - vanilla baseline and proposed SB update</t>
+          <t>Lourenço Marques - vanilla baseline and proposed SB update</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SB target mapping: Zambezi -&gt; STATE_ZAMBEZI | Vanilla proxy: Zambezi -&gt; STATE_ZAMBEZI</t>
+          <t>SB target mapping: Lourenço Marques -&gt; STATE_LOURENCO_MARQUES | Vanilla proxy: Lourenço Marques -&gt; STATE_LOURENCO_MARQUES</t>
         </is>
       </c>
     </row>
@@ -4555,7 +4577,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9">
@@ -4565,7 +4587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -4575,7 +4597,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-90</v>
+        <v>-104</v>
       </c>
     </row>
     <row r="11"/>
@@ -4630,10 +4652,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -4641,7 +4663,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-44</v>
+        <v>-49</v>
       </c>
     </row>
     <row r="15">
@@ -4662,17 +4684,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Unchanged</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>No change</t>
         </is>
       </c>
     </row>
@@ -4753,12 +4775,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4768,7 +4790,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>Removed</t>
         </is>
       </c>
     </row>
@@ -4886,17 +4908,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Unchanged</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>No change</t>
+          <t>Removed</t>
         </is>
       </c>
     </row>
@@ -4918,17 +4940,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Unchanged</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Removed</t>
+          <t>No change</t>
         </is>
       </c>
     </row>
@@ -4950,17 +4972,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Unchanged</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>No change</t>
+          <t>Removed</t>
         </is>
       </c>
     </row>
@@ -5014,17 +5036,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Unchanged</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>No change</t>
+          <t>Added</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5063,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5051,12 +5073,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Unchanged</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>No change</t>
+          <t>Removed</t>
         </is>
       </c>
     </row>
@@ -5136,14 +5158,14 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Exception</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -5162,18 +5184,18 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Exception</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="32">
@@ -5243,15 +5265,15 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Exception</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -5318,18 +5340,18 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Counterfactual</t>
+          <t>Exception</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="38">
@@ -5477,7 +5499,7 @@
         <v>16</v>
       </c>
       <c r="D43" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -5485,7 +5507,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5512,21 +5534,21 @@
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hereroland - vanilla baseline and proposed SB update</t>
+          <t>Zambezi - vanilla baseline and proposed SB update</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SB target mapping: Hereroland -&gt; STATE_HEREROLAND | Vanilla proxy: Hereroland -&gt; STATE_HEREROLAND</t>
+          <t>SB target mapping: Zambezi -&gt; STATE_ZAMBEZI | Vanilla proxy: Zambezi -&gt; STATE_ZAMBEZI</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5593,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>88</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9">
@@ -5581,7 +5603,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
@@ -5591,7 +5613,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-69</v>
+        <v>-89</v>
       </c>
     </row>
     <row r="11"/>
@@ -5646,18 +5668,18 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Counterfactual</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-36</v>
+        <v>-43</v>
       </c>
     </row>
     <row r="15">
@@ -5774,17 +5796,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Unchanged</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>No change</t>
+          <t>Added</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5855,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -5843,12 +5865,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Unchanged</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>No change</t>
         </is>
       </c>
     </row>
@@ -5865,12 +5887,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -5897,12 +5919,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -5929,7 +5951,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -5939,12 +5961,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Unchanged</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>No change</t>
+          <t>Removed</t>
         </is>
       </c>
     </row>
@@ -5961,12 +5983,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -5993,12 +6015,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -6152,14 +6174,14 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Exception</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -6178,18 +6200,18 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Exception</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -6259,7 +6281,7 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -6267,7 +6289,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -6311,7 +6333,7 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -6319,7 +6341,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -6334,18 +6356,18 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Exception</t>
+          <t>Counterfactual</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="38">
@@ -6490,18 +6512,18 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Exception</t>
+          <t>Counterfactual</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6528,6 +6550,1022 @@
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hereroland - vanilla baseline and proposed SB update</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SB target mapping: Hereroland -&gt; STATE_HEREROLAND | Vanilla proxy: Hereroland -&gt; STATE_HEREROLAND</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>The SB update column shows the current audited value. Basis shows whether the row is historical, bounded counterfactual, explicit exception, or unchanged baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Method summary: quantity rows use the GBR 1940 representative-year rule and a shared chronology Z based on earliest commercial activity year plus representative-year lag; Arable Land, Wood, and Rubber (undiscovered) use direct effective hectares.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Vanilla total</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SB update total</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Delta vs vanilla</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-69</v>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Resource rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Resource</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Vanilla baseline</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>SB update</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Delta / change</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Arable</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Arable Land</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>40</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>-36</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Arable Resource</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Wheat Farm</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Arable Resource</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Livestock Ranch</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Arable Resource</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Vineyard</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Arable Resource</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tea Plantation</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Arable Resource</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Maize Farm</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Arable Resource</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Millet Farm</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Arable Resource</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sugar Plantation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Arable Resource</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tobacco Plantation</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Arable Resource</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Banana Plantation</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Arable Resource</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Coffee Plantation</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Arable Resource</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cotton Plantation</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Arable Resource</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Rice Farm</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Arable Resource</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Dye Plantation</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Arable Resource</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Opium</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Arable Resource</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Silk Plantation</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Capped Resource</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Coal Mine</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>40</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Capped Resource</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>11</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Capped Resource</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Gold Mine</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Capped Resource</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Iron Mine</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Capped Resource</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Lead Mine</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Capped Resource</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sulfur Mine</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Capped Resource</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Whaling</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Capped Resource</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Special Resource</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Gold Fields (discovered)</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Special Resource</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Gold Fields (undiscovered)</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Special Resource</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Oil (discovered)</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Special Resource</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Oil (undiscovered)</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Special Resource</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Rubber (discovered)</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Special Resource</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Rubber (undiscovered)</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A4:F4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
@@ -6597,7 +7635,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -6607,7 +7645,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-69</v>
+        <v>-68</v>
       </c>
     </row>
     <row r="11"/>
@@ -6665,7 +7703,7 @@
         <v>30</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -6673,7 +7711,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-29</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="15">
@@ -7613,7 +8651,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
@@ -7623,7 +8661,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="11"/>
@@ -7681,7 +8719,7 @@
         <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -7689,7 +8727,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="15">
@@ -8629,7 +9667,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
@@ -8639,7 +9677,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-24</v>
+        <v>-23</v>
       </c>
     </row>
     <row r="11"/>
@@ -8697,7 +9735,7 @@
         <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -8705,7 +9743,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-29</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="15">
@@ -9645,7 +10683,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10">
@@ -9655,7 +10693,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-77</v>
+        <v>-74</v>
       </c>
     </row>
     <row r="11"/>
@@ -9713,7 +10751,7 @@
         <v>60</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -9721,7 +10759,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-15</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="15">
@@ -9838,17 +10876,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Unchanged</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>No change</t>
+          <t>Removed</t>
         </is>
       </c>
     </row>
@@ -10661,7 +11699,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10">
@@ -10671,7 +11709,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-116</v>
+        <v>-114</v>
       </c>
     </row>
     <row r="11"/>
@@ -10729,7 +11767,7 @@
         <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -10737,7 +11775,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-35</v>
+        <v>-33</v>
       </c>
     </row>
     <row r="15">
@@ -11677,7 +12715,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10">
@@ -11687,7 +12725,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-70</v>
+        <v>-69</v>
       </c>
     </row>
     <row r="11"/>
@@ -11745,7 +12783,7 @@
         <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -11753,7 +12791,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="15">
@@ -12693,7 +13731,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -12703,7 +13741,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-199</v>
+        <v>-197</v>
       </c>
     </row>
     <row r="11"/>
@@ -12761,7 +13799,7 @@
         <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -12769,7 +13807,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-32</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="15">
@@ -13709,7 +14747,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -13719,7 +14757,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-117</v>
+        <v>-115</v>
       </c>
     </row>
     <row r="11"/>
@@ -13777,7 +14815,7 @@
         <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -13785,7 +14823,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="15">
@@ -14656,21 +15694,21 @@
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Drakensberg - vanilla baseline and proposed SB update</t>
+          <t>Zululand - vanilla baseline and proposed SB update</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SB target mapping: Drakensberg -&gt; STATE_DRAKENSBERG | Vanilla proxy: Zululand -&gt; STATE_ZULULAND</t>
+          <t>SB target mapping: Zululand -&gt; STATE_ZULULAND | Vanilla proxy: Zululand -&gt; STATE_ZULULAND</t>
         </is>
       </c>
     </row>
@@ -14715,7 +15753,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9">
@@ -14725,7 +15763,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -14735,7 +15773,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-119</v>
+        <v>-61</v>
       </c>
     </row>
     <row r="11"/>
@@ -14790,18 +15828,18 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Counterfactual</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-31</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
@@ -14822,17 +15860,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Unchanged</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>No change</t>
         </is>
       </c>
     </row>
@@ -14881,7 +15919,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -14891,12 +15929,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Unchanged</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Removed</t>
+          <t>No change</t>
         </is>
       </c>
     </row>
@@ -14918,17 +15956,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Unchanged</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Removed</t>
+          <t>No change</t>
         </is>
       </c>
     </row>
@@ -15009,12 +16047,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -15041,12 +16079,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -15078,17 +16116,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Unchanged</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Removed</t>
+          <t>No change</t>
         </is>
       </c>
     </row>
@@ -15142,17 +16180,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Unchanged</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Removed</t>
+          <t>No change</t>
         </is>
       </c>
     </row>
@@ -15296,7 +16334,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -15307,7 +16345,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>-72</v>
+        <v>-48</v>
       </c>
     </row>
     <row r="31">
@@ -15322,7 +16360,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -15333,7 +16371,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="32">
@@ -15478,18 +16516,18 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Exception</t>
+          <t>Counterfactual</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-11</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="38">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -2202,14 +2202,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>not started</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -2223,14 +2223,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>not started</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98">
@@ -10876,17 +10876,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Unchanged</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Removed</t>
+          <t>No change</t>
         </is>
       </c>
     </row>

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -2244,14 +2244,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>not started</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -2265,14 +2265,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>not started</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -2286,14 +2286,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>not started</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -222,10 +222,10 @@
         <v>472</v>
       </c>
       <c r="C15">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D15">
-        <v>-347</v>
+        <v>-346</v>
       </c>
     </row>
     <row r="16">
@@ -238,10 +238,10 @@
         <v>45</v>
       </c>
       <c r="C16">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16">
-        <v>-15</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="17">
@@ -270,10 +270,10 @@
         <v>123</v>
       </c>
       <c r="C18">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18">
-        <v>-91</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="19">
@@ -1922,14 +1922,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">not started</t>
+          <t xml:space="preserve">accepted</t>
         </is>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103">
@@ -15260,7 +15260,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>-61</v>
+        <v>-58</v>
       </c>
     </row>
     <row r="12">
@@ -15833,15 +15833,15 @@
         <v>48</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exception</t>
+          <t xml:space="preserve">Historical</t>
         </is>
       </c>
       <c r="F30">
-        <v>-48</v>
+        <v>-47</v>
       </c>
     </row>
     <row r="31">
@@ -15859,15 +15859,15 @@
         <v>6</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exception</t>
+          <t xml:space="preserve">Historical</t>
         </is>
       </c>
       <c r="F31">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="32">
@@ -15911,15 +15911,15 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exception</t>
+          <t xml:space="preserve">Counterfactual</t>
         </is>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -238,10 +238,10 @@
         <v>45</v>
       </c>
       <c r="C16">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D16">
-        <v>-14</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="17">
@@ -1943,14 +1943,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">not started</t>
+          <t xml:space="preserve">accepted</t>
         </is>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104">
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>-118</v>
+        <v>-117</v>
       </c>
     </row>
     <row r="12">
@@ -2742,15 +2742,15 @@
         <v>5</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exception</t>
+          <t xml:space="preserve">Historical</t>
         </is>
       </c>
       <c r="F31">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="32">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -1964,14 +1964,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">not started</t>
+          <t xml:space="preserve">accepted</t>
         </is>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -1985,14 +1985,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">not started</t>
+          <t xml:space="preserve">accepted</t>
         </is>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -222,10 +222,10 @@
         <v>472</v>
       </c>
       <c r="C15">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D15">
-        <v>-346</v>
+        <v>-348</v>
       </c>
     </row>
     <row r="16">
@@ -302,10 +302,10 @@
         <v>0</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -366,10 +366,10 @@
         <v>36</v>
       </c>
       <c r="C24">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D24">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25">
@@ -2006,14 +2006,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">not started</t>
+          <t xml:space="preserve">accepted</t>
         </is>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="107">
@@ -5743,15 +5743,15 @@
         <v>44</v>
       </c>
       <c r="D30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Historical</t>
+          <t xml:space="preserve">Counterfactual</t>
         </is>
       </c>
       <c r="F30">
-        <v>-40</v>
+        <v>-42</v>
       </c>
     </row>
     <row r="31">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Historical</t>
+          <t xml:space="preserve">Counterfactual</t>
         </is>
       </c>
       <c r="F34">
@@ -5873,15 +5873,15 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exception</t>
+          <t xml:space="preserve">Counterfactual</t>
         </is>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -5977,7 +5977,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         </is>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -2027,14 +2027,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">not started</t>
+          <t xml:space="preserve">accepted</t>
         </is>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="108">
@@ -6111,7 +6111,7 @@
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Historical</t>
+          <t xml:space="preserve">Counterfactual</t>
         </is>
       </c>
       <c r="F31">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -1775,14 +1775,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">accepted</t>
+          <t xml:space="preserve">not started</t>
         </is>
       </c>
       <c r="D95">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E95">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">accepted</t>
+          <t xml:space="preserve">not started</t>
         </is>
       </c>
       <c r="D96">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E96">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -1817,14 +1817,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">accepted</t>
+          <t xml:space="preserve">not started</t>
         </is>
       </c>
       <c r="D97">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E97">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -1838,14 +1838,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">accepted</t>
+          <t xml:space="preserve">not started</t>
         </is>
       </c>
       <c r="D98">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E98">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -1859,14 +1859,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">accepted</t>
+          <t xml:space="preserve">not started</t>
         </is>
       </c>
       <c r="D99">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E99">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -1880,14 +1880,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">accepted</t>
+          <t xml:space="preserve">not started</t>
         </is>
       </c>
       <c r="D100">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E100">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -1901,14 +1901,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">accepted</t>
+          <t xml:space="preserve">not started</t>
         </is>
       </c>
       <c r="D101">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E101">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -1922,14 +1922,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">accepted</t>
+          <t xml:space="preserve">not started</t>
         </is>
       </c>
       <c r="D102">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E102">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -1943,14 +1943,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">accepted</t>
+          <t xml:space="preserve">not started</t>
         </is>
       </c>
       <c r="D103">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E103">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -1964,14 +1964,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">accepted</t>
+          <t xml:space="preserve">not started</t>
         </is>
       </c>
       <c r="D104">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E104">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -1985,14 +1985,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">accepted</t>
+          <t xml:space="preserve">not started</t>
         </is>
       </c>
       <c r="D105">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E105">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2006,14 +2006,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">accepted</t>
+          <t xml:space="preserve">not started</t>
         </is>
       </c>
       <c r="D106">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E106">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -2027,14 +2027,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">accepted</t>
+          <t xml:space="preserve">not started</t>
         </is>
       </c>
       <c r="D107">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E107">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Historical</t>
+          <t xml:space="preserve">Counterfactual</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Historical</t>
+          <t xml:space="preserve">Counterfactual</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -10147,7 +10147,7 @@
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10412,7 +10412,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unchanged</t>
+          <t xml:space="preserve">Counterfactual</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -1775,14 +1775,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">not started</t>
+          <t xml:space="preserve">accepted</t>
         </is>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">not started</t>
+          <t xml:space="preserve">accepted</t>
         </is>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97">
@@ -9526,17 +9526,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Historical</t>
+          <t xml:space="preserve">Unchanged</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Added</t>
+          <t xml:space="preserve">No change</t>
         </is>
       </c>
     </row>

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -1817,14 +1817,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">not started</t>
+          <t xml:space="preserve">accepted</t>
         </is>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -1838,14 +1838,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">not started</t>
+          <t xml:space="preserve">accepted</t>
         </is>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -1859,14 +1859,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">not started</t>
+          <t xml:space="preserve">accepted</t>
         </is>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E99">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -1880,14 +1880,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">not started</t>
+          <t xml:space="preserve">accepted</t>
         </is>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E100">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Historical</t>
+          <t xml:space="preserve">Counterfactual</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -1901,14 +1901,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">not started</t>
+          <t xml:space="preserve">accepted</t>
         </is>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="102">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -1922,14 +1922,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">not started</t>
+          <t xml:space="preserve">accepted</t>
         </is>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -1943,14 +1943,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">not started</t>
+          <t xml:space="preserve">accepted</t>
         </is>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -2006,14 +2006,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">not started</t>
+          <t xml:space="preserve">accepted</t>
         </is>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="107">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -2027,14 +2027,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">not started</t>
+          <t xml:space="preserve">accepted</t>
         </is>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="108">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -222,10 +222,10 @@
         <v>472</v>
       </c>
       <c r="C15">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D15">
-        <v>-348</v>
+        <v>-346</v>
       </c>
     </row>
     <row r="16">
@@ -238,10 +238,10 @@
         <v>45</v>
       </c>
       <c r="C16">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D16">
-        <v>-13</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="17">
@@ -270,10 +270,10 @@
         <v>123</v>
       </c>
       <c r="C18">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D18">
-        <v>-90</v>
+        <v>-87</v>
       </c>
     </row>
     <row r="19">
@@ -286,10 +286,10 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -334,10 +334,10 @@
         <v>71</v>
       </c>
       <c r="C22">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D22">
-        <v>-40</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="23">
@@ -1199,10 +1199,10 @@
         <v>123</v>
       </c>
       <c r="D66">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E66">
-        <v>-91</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="67">
@@ -1535,10 +1535,10 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E82">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -1598,10 +1598,10 @@
         <v>6</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="86">
@@ -2048,14 +2048,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">not started</t>
+          <t xml:space="preserve">accepted</t>
         </is>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>-117</v>
+        <v>-116</v>
       </c>
     </row>
     <row r="12">
@@ -2716,7 +2716,7 @@
         <v>72</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         </is>
       </c>
       <c r="F30">
-        <v>-72</v>
+        <v>-71</v>
       </c>
     </row>
     <row r="31">
@@ -2742,15 +2742,15 @@
         <v>5</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Historical</t>
+          <t xml:space="preserve">Exception</t>
         </is>
       </c>
       <c r="F31">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="32">
@@ -2898,7 +2898,7 @@
         <v>11</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         </is>
       </c>
       <c r="F37">
-        <v>-11</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="38">
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -3162,7 +3162,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>-86</v>
+        <v>-83</v>
       </c>
     </row>
     <row r="12">
@@ -3725,15 +3725,15 @@
         <v>48</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exception</t>
+          <t xml:space="preserve">Historical</t>
         </is>
       </c>
       <c r="F30">
-        <v>-48</v>
+        <v>-47</v>
       </c>
     </row>
     <row r="31">
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -3907,7 +3907,7 @@
         <v>5</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         </is>
       </c>
       <c r="F37">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="38">
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>-104</v>
+        <v>-103</v>
       </c>
     </row>
     <row r="12">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">no</t>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removed</t>
+          <t xml:space="preserve">No change</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
         <v>9</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="F37">
-        <v>-9</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="38">
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -5180,7 +5180,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>-89</v>
+        <v>-88</v>
       </c>
     </row>
     <row r="12">
@@ -5821,15 +5821,15 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exception</t>
+          <t xml:space="preserve">Historical</t>
         </is>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -6179,7 +6179,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>-69</v>
+        <v>-68</v>
       </c>
     </row>
     <row r="12">
@@ -6934,7 +6934,7 @@
         <v>2</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         </is>
       </c>
       <c r="F37">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="38">
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -7198,7 +7198,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>-68</v>
+        <v>-67</v>
       </c>
     </row>
     <row r="12">
@@ -7865,15 +7865,15 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exception</t>
+          <t xml:space="preserve">Historical</t>
         </is>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -14251,7 +14251,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -14261,7 +14261,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>-115</v>
+        <v>-114</v>
       </c>
     </row>
     <row r="12">
@@ -14902,7 +14902,7 @@
         <v>30</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         </is>
       </c>
       <c r="F33">
-        <v>-30</v>
+        <v>-29</v>
       </c>
     </row>
     <row r="34">

--- a/Docs/resources/RESOURCES.xlsx
+++ b/Docs/resources/RESOURCES.xlsx
@@ -2239,17 +2239,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Historical</t>
+          <t xml:space="preserve">Unchanged</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Added</t>
+          <t xml:space="preserve">No change</t>
         </is>
       </c>
     </row>
@@ -2399,17 +2399,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unchanged</t>
+          <t xml:space="preserve">Historical</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">No change</t>
+          <t xml:space="preserve">Removed</t>
         </is>
       </c>
     </row>
@@ -3376,17 +3376,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Historical</t>
+          <t xml:space="preserve">Unchanged</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Added</t>
+          <t xml:space="preserve">No change</t>
         </is>
       </c>
     </row>
@@ -4417,17 +4417,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unchanged</t>
+          <t xml:space="preserve">Historical</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">No change</t>
+          <t xml:space="preserve">Removed</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">No change</t>
+          <t xml:space="preserve">Removed</t>
         </is>
       </c>
     </row>
@@ -4609,17 +4609,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Historical</t>
+          <t xml:space="preserve">Unchanged</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Added</t>
+          <t xml:space="preserve">No change</t>
         </is>
       </c>
     </row>
@@ -5266,17 +5266,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Historical</t>
+          <t xml:space="preserve">Unchanged</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Added</t>
+          <t xml:space="preserve">No change</t>
         </is>
       </c>
     </row>
@@ -5426,17 +5426,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unchanged</t>
+          <t xml:space="preserve">Historical</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">No change</t>
+          <t xml:space="preserve">Removed</t>
         </is>
       </c>
     </row>
@@ -6275,17 +6275,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Historical</t>
+          <t xml:space="preserve">Unchanged</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Added</t>
+          <t xml:space="preserve">No change</t>
         </is>
       </c>
     </row>
@@ -6403,17 +6403,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Historical</t>
+          <t xml:space="preserve">Unchanged</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Added</t>
+          <t xml:space="preserve">No change</t>
         </is>
       </c>
     </row>
@@ -9430,17 +9430,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Historical</t>
+          <t xml:space="preserve">Unchanged</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Added</t>
+          <t xml:space="preserve">No change</t>
         </is>
       </c>
     </row>
@@ -9462,17 +9462,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Historical</t>
+          <t xml:space="preserve">Unchanged</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Added</t>
+          <t xml:space="preserve">No change</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10311,17 +10311,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unchanged</t>
+          <t xml:space="preserve">Historical</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">No change</t>
+          <t xml:space="preserve">Removed</t>
         </is>
       </c>
     </row>
@@ -10407,17 +10407,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Counterfactual</t>
+          <t xml:space="preserve">Historical</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">No change</t>
+          <t xml:space="preserve">Removed</t>
         </is>
       </c>
     </row>
@@ -11480,17 +11480,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unchanged</t>
+          <t xml:space="preserve">Historical</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">No change</t>
+          <t xml:space="preserve">Removed</t>
         </is>
       </c>
     </row>
@@ -14347,17 +14347,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Historical</t>
+          <t xml:space="preserve">Unchanged</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Added</t>
+          <t xml:space="preserve">No change</t>
         </is>
       </c>
     </row>
@@ -15516,17 +15516,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">no</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unchanged</t>
+          <t xml:space="preserve">Historical</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">No change</t>
+          <t xml:space="preserve">Removed</t>
         </is>
       </c>
     </row>
